--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2011/KENTUCKY_2011.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2011/KENTUCKY_2011.xlsx
@@ -2418,7 +2418,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Gral. Simon Boivar</t>
+          <t>Gral. Simon Bolivar</t>
         </is>
       </c>
       <c r="C115">
@@ -2634,7 +2634,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C127">
@@ -7044,7 +7044,7 @@
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>Dr. Arroyo</t>
+          <t>Doctor Arroyo</t>
         </is>
       </c>
       <c r="C372">
@@ -11670,7 +11670,7 @@
       </c>
       <c r="B629" t="inlineStr">
         <is>
-          <t>Tuxpam</t>
+          <t>Tuxpan</t>
         </is>
       </c>
       <c r="C629">
